--- a/data/trans_orig/IP19-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP19-Edad-trans_orig.xlsx
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>102008</t>
+          <t>101662</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>118318</t>
+          <t>118121</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>222544</t>
+          <t>222163</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>4509</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>3259</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>185306</t>
+          <t>186647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>206814</t>
+          <t>206886</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>188727</t>
+          <t>187540</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>209611</t>
+          <t>208755</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>381395</t>
+          <t>380433</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>409850</t>
+          <t>410265</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,93%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46391</t>
+          <t>46319</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67899</t>
+          <t>66558</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44145</t>
+          <t>45001</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65029</t>
+          <t>66216</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97111</t>
+          <t>96696</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125566</t>
+          <t>126528</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50501</t>
+          <t>50398</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67916</t>
+          <t>67759</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62139</t>
+          <t>61962</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81266</t>
+          <t>81289</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>118011</t>
+          <t>117939</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>144139</t>
+          <t>144745</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,8%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59632</t>
+          <t>59789</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77047</t>
+          <t>77150</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60249</t>
+          <t>60226</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79376</t>
+          <t>79553</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>124924</t>
+          <t>124318</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>151052</t>
+          <t>151124</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>56,17%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86954</t>
+          <t>87270</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>108868</t>
+          <t>109344</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>107319</t>
+          <t>107791</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>129482</t>
+          <t>130202</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>202116</t>
+          <t>200721</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>233403</t>
+          <t>233833</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,54%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>84538</t>
+          <t>84062</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>106452</t>
+          <t>106136</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>76567</t>
+          <t>75847</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>98730</t>
+          <t>98258</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>166052</t>
+          <t>165622</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>197339</t>
+          <t>198734</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,75%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>439339</t>
+          <t>439213</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>479666</t>
+          <t>479624</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>489331</t>
+          <t>490910</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>529620</t>
+          <t>529383</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>938291</t>
+          <t>940082</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>997450</t>
+          <t>994693</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>70,9%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>200664</t>
+          <t>200706</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>240991</t>
+          <t>241117</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>193080</t>
+          <t>193317</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>233369</t>
+          <t>231790</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>405580</t>
+          <t>408337</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>464739</t>
+          <t>462948</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,0%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>141598</t>
+          <t>141643</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>146138</t>
+          <t>146149</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>140924</t>
+          <t>140267</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>284285</t>
+          <t>284064</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>612</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2997</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6397</t>
+          <t>6618</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>169864</t>
+          <t>170939</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>191199</t>
+          <t>192324</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>185160</t>
+          <t>185699</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>210109</t>
+          <t>209246</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>364944</t>
+          <t>362183</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>396379</t>
+          <t>395842</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,46%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45051</t>
+          <t>43926</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66386</t>
+          <t>65311</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58138</t>
+          <t>59001</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83087</t>
+          <t>82548</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>108118</t>
+          <t>108655</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>139553</t>
+          <t>142314</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,21%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64715</t>
+          <t>64381</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84884</t>
+          <t>84769</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75156</t>
+          <t>75433</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96080</t>
+          <t>96061</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>145194</t>
+          <t>144437</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>173867</t>
+          <t>173311</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>54,91%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72159</t>
+          <t>72274</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92328</t>
+          <t>92662</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62491</t>
+          <t>62510</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>83415</t>
+          <t>83138</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>141747</t>
+          <t>142303</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>170420</t>
+          <t>171177</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,24%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79038</t>
+          <t>80486</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>101077</t>
+          <t>101672</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>94720</t>
+          <t>93956</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>115339</t>
+          <t>116040</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>180774</t>
+          <t>179713</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>211688</t>
+          <t>211182</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,34%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70260</t>
+          <t>69665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>92299</t>
+          <t>90851</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>63323</t>
+          <t>62622</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>83942</t>
+          <t>84706</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>138311</t>
+          <t>138817</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>169225</t>
+          <t>170286</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,65%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>471952</t>
+          <t>473942</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>511484</t>
+          <t>513269</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>511552</t>
+          <t>512186</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>551823</t>
+          <t>552389</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>996899</t>
+          <t>992301</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1052203</t>
+          <t>1050824</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>71,94%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>199907</t>
+          <t>198122</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>239439</t>
+          <t>237449</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>197577</t>
+          <t>197011</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>237848</t>
+          <t>237214</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>408588</t>
+          <t>409967</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>463892</t>
+          <t>468490</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,07%</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>120969</t>
+          <t>120959</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>252599</t>
+          <t>252014</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3804</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>154237</t>
+          <t>153595</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>174010</t>
+          <t>173353</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>190215</t>
+          <t>190623</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>211658</t>
+          <t>212110</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>350851</t>
+          <t>351086</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>380906</t>
+          <t>379092</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>80,9%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36507</t>
+          <t>37164</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56280</t>
+          <t>56922</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46403</t>
+          <t>45951</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>67846</t>
+          <t>67438</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87672</t>
+          <t>89486</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117727</t>
+          <t>117492</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94122</t>
+          <t>94955</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>116715</t>
+          <t>117540</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>90501</t>
+          <t>90328</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113505</t>
+          <t>113340</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>193133</t>
+          <t>191645</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>225282</t>
+          <t>224092</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,37%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72184</t>
+          <t>71359</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>94777</t>
+          <t>93944</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75067</t>
+          <t>75232</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>98071</t>
+          <t>98244</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>152189</t>
+          <t>153379</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>184338</t>
+          <t>185826</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>49,23%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77267</t>
+          <t>77725</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>99819</t>
+          <t>100172</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>95529</t>
+          <t>95917</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>117562</t>
+          <t>116750</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>177953</t>
+          <t>179587</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>211071</t>
+          <t>212983</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>61,32%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>73482</t>
+          <t>73129</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>96034</t>
+          <t>95576</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>56486</t>
+          <t>57298</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>78519</t>
+          <t>78131</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>136277</t>
+          <t>134365</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>169395</t>
+          <t>167761</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,3%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>470050</t>
+          <t>472836</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>510744</t>
+          <t>511918</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>511555</t>
+          <t>514544</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>553440</t>
+          <t>555616</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>993598</t>
+          <t>996012</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1054991</t>
+          <t>1053025</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,66%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>193627</t>
+          <t>192453</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>234321</t>
+          <t>231535</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>191404</t>
+          <t>189228</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>233289</t>
+          <t>230300</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>394224</t>
+          <t>396190</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>455617</t>
+          <t>453203</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47903</t>
+          <t>47719</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54328</t>
+          <t>54408</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>49299</t>
+          <t>49074</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57544</t>
+          <t>57593</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99567</t>
+          <t>99350</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110245</t>
+          <t>110082</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,54%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>857</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5298</t>
+          <t>5262</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>1788</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9077</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13161</t>
+          <t>12793</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>773</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6473</t>
+          <t>6476</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5689</t>
+          <t>5596</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8887</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77103</t>
+          <t>77579</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>97231</t>
+          <t>97360</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>84735</t>
+          <t>83810</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>106681</t>
+          <t>106767</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>167481</t>
+          <t>167660</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>197610</t>
+          <t>199413</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>59,53%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23662</t>
+          <t>24101</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40385</t>
+          <t>41058</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38468</t>
+          <t>38073</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59695</t>
+          <t>60843</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>67300</t>
+          <t>66142</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>93673</t>
+          <t>94964</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,35%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28130</t>
+          <t>29104</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46316</t>
+          <t>46433</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27141</t>
+          <t>26655</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45422</t>
+          <t>44566</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58901</t>
+          <t>59773</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84919</t>
+          <t>84680</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,28%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35391</t>
+          <t>36369</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>54975</t>
+          <t>56548</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29505</t>
+          <t>28867</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>50476</t>
+          <t>50627</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>70639</t>
+          <t>69219</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>99748</t>
+          <t>99202</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60367</t>
+          <t>60498</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85075</t>
+          <t>83831</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66086</t>
+          <t>67001</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95678</t>
+          <t>95319</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>133947</t>
+          <t>135505</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>171481</t>
+          <t>170713</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,14%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42041</t>
+          <t>42267</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>63339</t>
+          <t>62967</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75951</t>
+          <t>74940</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>104311</t>
+          <t>103689</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>124830</t>
+          <t>125948</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>160668</t>
+          <t>160362</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,4%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21101</t>
+          <t>20868</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49959</t>
+          <t>51152</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31357</t>
+          <t>31197</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63062</t>
+          <t>60711</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57133</t>
+          <t>56859</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>99930</t>
+          <t>101061</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>123990</t>
+          <t>123679</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>185070</t>
+          <t>181947</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>128554</t>
+          <t>125902</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>169885</t>
+          <t>167129</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>259729</t>
+          <t>262039</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>334998</t>
+          <t>341957</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>59,5%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>66150</t>
+          <t>69280</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>116743</t>
+          <t>116471</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>87751</t>
+          <t>89402</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>131286</t>
+          <t>133657</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>174081</t>
+          <t>171416</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>237254</t>
+          <t>237325</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,3%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>183798</t>
+          <t>183500</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236687</t>
+          <t>237122</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>208229</t>
+          <t>204326</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>259232</t>
+          <t>256473</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>410612</t>
+          <t>409931</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>482949</t>
+          <t>482342</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,32%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>222501</t>
+          <t>224188</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>304187</t>
+          <t>311047</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>253174</t>
+          <t>256510</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>310574</t>
+          <t>309886</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>494285</t>
+          <t>496703</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>597464</t>
+          <t>596245</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,42%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>162474</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>211914</t>
+          <t>212413</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>210840</t>
+          <t>210294</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>268717</t>
+          <t>266762</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>384559</t>
+          <t>384336</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>459488</t>
+          <t>461143</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP19-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>120730</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>117884</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,12%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>105325</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>101662</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>101554</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,2%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,75%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,65%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>120730</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>118121</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,31%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>342</t>
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>222163</t>
+          <t>222300</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -954,102 +954,102 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3496</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>846</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4509</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4617</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0,8%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>4,35%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>1496</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>3259</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>5251</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1496</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>5388</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -1062,57 +1062,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1292,72 +1292,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>199590</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>188258</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>209916</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>78,65%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>74,19%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>82,72%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>296</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>196543</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>186647</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>206886</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>185534</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>207137</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>77,62%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>73,71%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>81,71%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>199590</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>187540</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>208755</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>78,65%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>380433</t>
+          <t>381395</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>410265</t>
+          <t>409835</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>80,84%</t>
         </is>
       </c>
     </row>
@@ -1405,72 +1405,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>54166</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>43840</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>65498</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>21,35%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>17,28%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>25,81%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>56662</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>46319</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>66558</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>46068</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>67671</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>22,38%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18,29%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>26,29%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>54166</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>45001</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>66216</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>21,35%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96696</t>
+          <t>97126</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>126528</t>
+          <t>125566</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -1518,57 +1518,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1748,72 +1748,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>71689</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>62602</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>81198</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>50,66%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>44,24%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>57,38%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>58896</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>50398</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>67759</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>49126</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>67205</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>46,18%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>39,51%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>53,12%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>71689</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>61962</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>81289</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>50,66%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>117939</t>
+          <t>117538</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>144745</t>
+          <t>143175</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,21%</t>
         </is>
       </c>
     </row>
@@ -1861,72 +1861,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>69826</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>60317</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>78913</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>49,34%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>42,62%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>55,76%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>68652</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>59789</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>77150</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>60343</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>78422</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>53,82%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>46,88%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>60,49%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>69826</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>60226</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>79553</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>49,34%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>124318</t>
+          <t>125888</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>151124</t>
+          <t>151525</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,32%</t>
         </is>
       </c>
     </row>
@@ -1974,57 +1974,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2204,72 +2204,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>119367</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>108498</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>130973</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>57,93%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>52,66%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>63,56%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>98255</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>87270</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>109344</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>87333</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>109606</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>50,8%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>45,12%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>56,54%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>119367</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>107791</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>130202</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>57,93%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>200721</t>
+          <t>200477</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>233833</t>
+          <t>231470</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>57,95%</t>
         </is>
       </c>
     </row>
@@ -2317,72 +2317,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>86682</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>75076</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>97551</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>42,07%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>36,44%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>47,34%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>95151</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>84062</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>106136</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>83800</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>106073</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>49,2%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>43,46%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>54,88%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>86682</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>75847</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>98258</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>42,07%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>165622</t>
+          <t>167985</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>198734</t>
+          <t>198978</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>49,81%</t>
         </is>
       </c>
     </row>
@@ -2430,57 +2430,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>193406</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>193406</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>193406</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2660,72 +2660,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>511376</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>491898</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>530917</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>70,76%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>68,06%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>73,46%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>692</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>459019</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>439213</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>479624</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>438868</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>476981</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>67,47%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>64,56%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>70,5%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>511376</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>490910</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>529383</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>70,76%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>940082</t>
+          <t>942885</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>994693</t>
+          <t>997250</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,08%</t>
         </is>
       </c>
     </row>
@@ -2773,72 +2773,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>211324</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>191783</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>230802</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>29,24%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>26,54%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>31,94%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>325</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>221311</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>200706</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>241117</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>203349</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>241462</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>32,53%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>29,5%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>35,44%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>211324</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>193317</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>231790</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>29,24%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>408337</t>
+          <t>405780</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>462948</t>
+          <t>460145</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,8%</t>
         </is>
       </c>
     </row>
@@ -2886,57 +2886,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1017</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>680330</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>680330</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>680330</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3056,7 +3056,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3067,7 +3067,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3348,74 +3348,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>143252</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>140807</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>143921</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,54%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,84%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>144853</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>141643</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>146149</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>141589</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>146143</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,7%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,51%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>96,48%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>99,58%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>143252</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>140267</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>143921</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,54%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,46%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>419</t>
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>284064</t>
+          <t>284245</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>290020</t>
+          <t>290025</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3461,72 +3461,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3114</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1908</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5118</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5172</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>1,3%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,42%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>3654</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>657</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6618</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -3574,57 +3574,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>143921</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>143921</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>143921</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>146761</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>146761</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>146761</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>143921</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>143921</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>143921</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3804,72 +3804,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>197750</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>184355</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>208797</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>73,72%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>68,73%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>77,84%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>263</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>181917</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>170939</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>192324</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>171078</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>191409</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>77,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>72,36%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>81,41%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>197750</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>185699</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>209246</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>73,72%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>362183</t>
+          <t>363144</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>395842</t>
+          <t>395710</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -3917,72 +3917,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>70497</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>59450</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>83892</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>26,28%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>22,16%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>31,27%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>54333</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>43926</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>65311</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>44841</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>65172</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>23,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18,59%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>27,64%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>70497</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>59001</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>82548</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>26,28%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>108655</t>
+          <t>108787</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>142314</t>
+          <t>141353</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,02%</t>
         </is>
       </c>
     </row>
@@ -4030,57 +4030,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>268247</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>268247</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>268247</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>236250</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>268247</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>268247</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>268247</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4260,72 +4260,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>85689</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>75495</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>96353</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>54,04%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>47,61%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>60,76%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>74695</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>64381</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>84769</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>64540</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>85547</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>47,56%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>41,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>53,98%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>85689</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>75433</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>96061</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>54,04%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>144437</t>
+          <t>147162</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>173311</t>
+          <t>174184</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>55,19%</t>
         </is>
       </c>
     </row>
@@ -4373,72 +4373,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>72882</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>62218</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>83076</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>45,96%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>39,24%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>52,39%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>82348</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>72274</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>92662</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>71496</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>92503</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>52,44%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>46,02%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>59,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>72882</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>62510</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>83138</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>45,96%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>142303</t>
+          <t>141430</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>171177</t>
+          <t>168452</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>53,37%</t>
         </is>
       </c>
     </row>
@@ -4486,57 +4486,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>157043</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4716,72 +4716,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>105306</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>94990</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>116193</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>58,94%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>53,17%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>65,04%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>90879</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>80486</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>101672</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>80773</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>102039</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>53,04%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>46,98%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>59,34%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>105306</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>93956</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>116040</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>58,94%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>179713</t>
+          <t>180898</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>211182</t>
+          <t>212315</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,66%</t>
         </is>
       </c>
     </row>
@@ -4829,72 +4829,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>73356</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>62469</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>83672</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>41,06%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>34,96%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>46,83%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>80458</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>69665</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>90851</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>69298</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>90564</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>46,96%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>40,66%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>53,02%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>73356</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>62622</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>84706</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>41,06%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>138817</t>
+          <t>137684</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>170286</t>
+          <t>169101</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,31%</t>
         </is>
       </c>
     </row>
@@ -4942,57 +4942,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>178662</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>178662</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>178662</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>178662</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>178662</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>178662</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5172,72 +5172,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>531997</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>513172</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>552398</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>70,99%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>68,48%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>73,71%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>711</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>492345</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>473942</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>513269</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>471770</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>512632</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>69,21%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>66,62%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>72,15%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>760</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>531997</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>512186</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>552389</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>70,99%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>992301</t>
+          <t>997221</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1050824</t>
+          <t>1053005</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>72,08%</t>
         </is>
       </c>
     </row>
@@ -5285,72 +5285,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>217403</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>197002</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>236228</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>29,01%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>26,29%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>31,52%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>314</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>219046</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>198122</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>237449</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>198759</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>239621</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>30,79%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>27,85%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>33,38%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>217403</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>197011</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>237214</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>29,01%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>409967</t>
+          <t>407786</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>468490</t>
+          <t>463570</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,73%</t>
         </is>
       </c>
     </row>
@@ -5398,57 +5398,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1068</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>749400</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>749400</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>749400</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1025</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>711391</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1068</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>749400</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>749400</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>749400</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5568,7 +5568,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5579,7 +5579,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5860,74 +5860,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>123530</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>120341</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,92%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>123530</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>120959</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,42%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>397</t>
@@ -5940,7 +5940,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>252014</t>
+          <t>252646</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5973,107 +5973,107 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>634</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>3205</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>3172</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>3804</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -6086,57 +6086,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6316,107 +6316,107 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>201650</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>188796</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212166</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>78,14%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>73,16%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>82,22%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>164487</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>153595</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>173353</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>154306</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>173131</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>78,13%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>72,96%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>82,35%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>201650</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>190623</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212110</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>73,3%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>82,24%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>561</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>366137</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>351640</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>381316</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>78,14%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>73,87%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>82,19%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>561</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>366137</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>351086</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>379092</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>78,14%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,38%</t>
         </is>
       </c>
     </row>
@@ -6429,107 +6429,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>56411</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>45895</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>69265</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>21,86%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>17,78%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>26,84%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>46030</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>37164</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>56922</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>37386</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>56211</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>21,87%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>17,65%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>27,04%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>56411</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>45951</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>67438</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>17,76%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>26,7%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>102441</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>87262</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>116938</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>21,86%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>17,81%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>26,13%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>102441</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>89486</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>117492</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>21,86%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -6542,57 +6542,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6772,72 +6772,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>102140</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>91389</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>114121</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>54,17%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>48,46%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>60,52%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>105980</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>94955</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>117540</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>93585</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>116499</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>56,1%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>50,27%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>62,22%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>102140</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>90328</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>113340</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>54,17%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>191645</t>
+          <t>191636</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>224092</t>
+          <t>223068</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,1%</t>
         </is>
       </c>
     </row>
@@ -6885,72 +6885,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>86432</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>74451</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>97183</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>45,83%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>39,48%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>51,54%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>82919</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>71359</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>93944</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>72400</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>95314</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>43,9%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>37,78%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>49,73%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>86432</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>75232</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>98244</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>45,83%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>153379</t>
+          <t>154403</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>185826</t>
+          <t>185835</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6998,57 +6998,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7228,72 +7228,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>106811</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>95900</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>117585</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>61,37%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>55,1%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>67,56%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>88954</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>77725</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>100172</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>76653</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>99553</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>51,33%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>44,85%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>57,8%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>106811</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>95917</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>116750</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>61,37%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>179587</t>
+          <t>180534</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>212983</t>
+          <t>211513</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>60,89%</t>
         </is>
       </c>
     </row>
@@ -7341,72 +7341,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>67237</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>56463</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>78148</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>38,63%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>32,44%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>44,9%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>84347</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>73129</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>95576</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>73748</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>96648</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>48,67%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>42,2%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>55,15%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>67237</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>57298</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>78131</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>38,63%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>134365</t>
+          <t>135835</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>167761</t>
+          <t>166814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,03%</t>
         </is>
       </c>
     </row>
@@ -7454,57 +7454,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7684,72 +7684,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>774</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>534131</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>512830</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>553813</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>71,71%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>68,85%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>74,35%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>750</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>491075</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>472836</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>511918</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>472227</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>511627</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>69,72%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>67,13%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>72,68%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>774</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>534131</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>514544</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>555616</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>71,71%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>996012</t>
+          <t>998348</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1053025</t>
+          <t>1055137</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,81%</t>
         </is>
       </c>
     </row>
@@ -7797,72 +7797,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>210713</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>191031</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>232014</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>28,29%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>25,65%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>31,15%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>311</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>213296</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>192453</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>231535</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>192744</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>232144</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>30,28%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>27,32%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>32,87%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>210713</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>189228</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>230300</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>28,29%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>396190</t>
+          <t>394078</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>453203</t>
+          <t>450867</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -7910,57 +7910,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8080,7 +8080,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -8091,7 +8091,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -8259,72 +8259,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>44611</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>40727</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>47259</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>88,9%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>81,16%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>94,18%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>51714</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>47719</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>54408</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>91,26%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>84,21%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>96,01%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>54145</t>
+          <t>46017</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>49074</t>
+          <t>41682</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57593</t>
+          <t>48659</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,32 +8334,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>105858</t>
+          <t>90629</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99350</t>
+          <t>85544</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110082</t>
+          <t>94636</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,15%</t>
         </is>
       </c>
     </row>
@@ -8372,72 +8372,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3859</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1635</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7606</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>7,69%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>15,16%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2440</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>857</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5262</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>9,28%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4821</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>7261</t>
+          <t>6771</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>3721</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12793</t>
+          <t>11443</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -8485,72 +8485,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1709</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4796</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>9,56%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2516</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>773</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6476</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,43%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>2488</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>794</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1780</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9050</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -8598,57 +8598,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>50180</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>50180</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>50180</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>56670</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>56670</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>56670</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>61018</t>
+          <t>51417</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61018</t>
+          <t>51417</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61018</t>
+          <t>51417</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>117687</t>
+          <t>101597</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>117687</t>
+          <t>101597</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>117687</t>
+          <t>101597</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8715,72 +8715,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>82091</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>71502</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>91470</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>52,93%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>46,1%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>58,98%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>87238</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>77579</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>97360</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>56,27%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>50,04%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>62,8%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>95988</t>
+          <t>77398</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>83810</t>
+          <t>67681</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>106767</t>
+          <t>87477</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,32 +8790,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>183226</t>
+          <t>159488</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>167660</t>
+          <t>145588</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>199413</t>
+          <t>172415</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>57,96%</t>
         </is>
       </c>
     </row>
@@ -8828,72 +8828,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>42152</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>33069</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>52314</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>27,18%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>21,32%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>33,73%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>31340</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>24101</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>41058</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>20,21%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>15,54%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>26,48%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48507</t>
+          <t>28808</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38073</t>
+          <t>21941</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>60843</t>
+          <t>36869</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>79847</t>
+          <t>70960</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>66142</t>
+          <t>60066</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>94964</t>
+          <t>84678</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,47%</t>
         </is>
       </c>
     </row>
@@ -8941,72 +8941,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>30853</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23470</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>39423</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>19,89%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15,13%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>25,42%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>36465</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>29104</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>46433</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>23,52%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18,77%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>29,95%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>35430</t>
+          <t>36170</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26655</t>
+          <t>27913</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44566</t>
+          <t>45064</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>71895</t>
+          <t>67023</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59773</t>
+          <t>56593</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84680</t>
+          <t>79561</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -9054,57 +9054,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>155095</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>155095</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>155095</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>251</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>155043</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>155043</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>155043</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>179925</t>
+          <t>142377</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>179925</t>
+          <t>142377</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>179925</t>
+          <t>142377</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>334968</t>
+          <t>297471</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>334968</t>
+          <t>297471</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>334968</t>
+          <t>297471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9171,72 +9171,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35803</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>27263</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>46579</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>18,18%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>13,85%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>23,66%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>45378</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>36369</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>56548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>26,84%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>21,51%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>33,45%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>38568</t>
+          <t>46862</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28867</t>
+          <t>37259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>50627</t>
+          <t>57504</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9246,32 +9246,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>83946</t>
+          <t>82666</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>69219</t>
+          <t>68383</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>99202</t>
+          <t>96959</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -9284,72 +9284,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>76194</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>62217</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>88479</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>38,7%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>31,6%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>44,94%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>71993</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>60498</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>83831</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>42,59%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>35,79%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>49,59%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>80584</t>
+          <t>70178</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67001</t>
+          <t>58937</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95319</t>
+          <t>81292</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>152577</t>
+          <t>146372</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>135505</t>
+          <t>128184</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>170713</t>
+          <t>163583</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>44,55%</t>
         </is>
       </c>
     </row>
@@ -9397,72 +9397,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>84900</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>72423</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>99483</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>43,12%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>36,78%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>50,53%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>51683</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>42267</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>62967</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>37,25%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>89994</t>
+          <t>53292</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>74940</t>
+          <t>43000</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>103689</t>
+          <t>64526</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>141676</t>
+          <t>138192</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>125948</t>
+          <t>120990</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>160362</t>
+          <t>155436</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -9510,57 +9510,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>196897</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>196897</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>196897</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>169054</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>169054</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>169054</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>209146</t>
+          <t>170332</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>209146</t>
+          <t>170332</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>209146</t>
+          <t>170332</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>378200</t>
+          <t>367230</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>378200</t>
+          <t>367230</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>378200</t>
+          <t>367230</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9627,72 +9627,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>35599</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>25950</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>46752</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>12,4%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>9,04%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>16,28%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>31471</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>20868</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>51152</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>11,47%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,6%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>18,64%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>43397</t>
+          <t>28159</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31197</t>
+          <t>20029</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60711</t>
+          <t>37494</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>74867</t>
+          <t>63757</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>56859</t>
+          <t>51340</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101061</t>
+          <t>79096</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -9740,72 +9740,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>148525</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>130835</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>167372</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>51,72%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>45,56%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>58,29%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>144388</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>123679</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>181947</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>52,62%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>45,07%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>66,31%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>148917</t>
+          <t>125763</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>125902</t>
+          <t>111097</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>167129</t>
+          <t>140568</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>293305</t>
+          <t>274288</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>262039</t>
+          <t>248459</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>341957</t>
+          <t>297313</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>54,8%</t>
         </is>
       </c>
     </row>
@@ -9853,72 +9853,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>103037</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>85165</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>122094</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>35,88%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>29,66%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>42,52%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>98549</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>69280</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>116471</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>35,91%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>25,25%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>42,44%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>107969</t>
+          <t>101474</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>89402</t>
+          <t>87818</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>133657</t>
+          <t>116203</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>206518</t>
+          <t>204512</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>171416</t>
+          <t>181757</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>237325</t>
+          <t>229935</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>42,38%</t>
         </is>
       </c>
     </row>
@@ -9966,57 +9966,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>287161</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>287161</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>287161</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>274408</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>274408</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>274408</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>300283</t>
+          <t>255396</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>300283</t>
+          <t>255396</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>300283</t>
+          <t>255396</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>574691</t>
+          <t>542558</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>574691</t>
+          <t>542558</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>574691</t>
+          <t>542558</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10083,72 +10083,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>198104</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>179474</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>220135</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>28,74%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>26,04%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>31,93%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>345</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>215801</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>183500</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>237122</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>32,94%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>28,01%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>36,19%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>232097</t>
+          <t>198436</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>204326</t>
+          <t>179349</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>256473</t>
+          <t>218221</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>447898</t>
+          <t>396540</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>409931</t>
+          <t>367710</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>482342</t>
+          <t>424287</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>32,42%</t>
         </is>
       </c>
     </row>
@@ -10196,72 +10196,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>270730</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>246452</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>296043</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>39,27%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>35,75%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>42,95%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>315</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>250161</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>224188</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>311047</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>38,18%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>34,22%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>47,48%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>282829</t>
+          <t>227662</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256510</t>
+          <t>207187</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>309886</t>
+          <t>249535</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>532991</t>
+          <t>498391</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>496703</t>
+          <t>465133</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>596245</t>
+          <t>534515</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>40,84%</t>
         </is>
       </c>
     </row>
@@ -10309,72 +10309,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>220500</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>194283</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>245630</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>31,99%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>28,18%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>35,63%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>268</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>189213</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>160100</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>212413</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>28,88%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>24,44%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>32,42%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>235444</t>
+          <t>193425</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>210294</t>
+          <t>173608</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>266762</t>
+          <t>213379</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>424657</t>
+          <t>413924</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>384336</t>
+          <t>383023</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>461143</t>
+          <t>448051</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>34,23%</t>
         </is>
       </c>
     </row>
@@ -10422,57 +10422,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>963</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>689334</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>689334</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>689334</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>928</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>655175</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>655175</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>655175</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>963</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>750371</t>
+          <t>619523</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>750371</t>
+          <t>619523</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>750371</t>
+          <t>619523</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1405546</t>
+          <t>1308856</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1405546</t>
+          <t>1308856</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1405546</t>
+          <t>1308856</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
